--- a/docs/COMPETITIVE_ANALYSIS_MATRIX.xlsx
+++ b/docs/COMPETITIVE_ANALYSIS_MATRIX.xlsx
@@ -1568,6 +1568,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -2454,6 +2455,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
@@ -3908,6 +3910,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
@@ -4939,7 +4942,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Currency detection (30+)</t>
+          <t>Currency detection (27)</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -5365,7 +5368,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Social media extraction (6)</t>
+          <t>Social media extraction (5)</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -5504,6 +5507,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
@@ -6816,6 +6820,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
@@ -7844,6 +7849,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
@@ -8591,7 +8597,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Currency handling (30+)</t>
+          <t>Currency handling (27)</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
